--- a/data/trans_orig/P1438_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1438_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de otro dolor crónico en 2023</t>
+          <t>Población con diagnóstico de otro dolor crónico en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2746</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4435</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10193</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2746</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9335</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>9342</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2746</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>9697</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>303865</t>
+          <t>303007</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>703490</t>
+          <t>703845</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2437</t>
+          <t>2397</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15244</t>
+          <t>15196</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15528</t>
+          <t>16391</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>7424</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25358</t>
+          <t>25756</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>408303</t>
+          <t>408351</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>421110</t>
+          <t>421150</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>495976</t>
+          <t>495113</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>508438</t>
+          <t>508027</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>909693</t>
+          <t>909295</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>927621</t>
+          <t>927627</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11710</t>
+          <t>11981</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28697</t>
+          <t>29078</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15803</t>
+          <t>15799</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30549</t>
+          <t>30647</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30848</t>
+          <t>31643</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53386</t>
+          <t>53836</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>507641</t>
+          <t>507260</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>524628</t>
+          <t>524357</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>511250</t>
+          <t>511152</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>525996</t>
+          <t>526000</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1024751</t>
+          <t>1024301</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1047289</t>
+          <t>1046494</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13728</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51509</t>
+          <t>51704</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38272</t>
+          <t>37557</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59963</t>
+          <t>59632</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48841</t>
+          <t>50360</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103563</t>
+          <t>105726</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>836277</t>
+          <t>836082</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>874058</t>
+          <t>874275</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>652535</t>
+          <t>652866</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>674226</t>
+          <t>674941</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1496722</t>
+          <t>1494559</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1551444</t>
+          <t>1549925</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21324</t>
+          <t>20616</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40549</t>
+          <t>40261</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50940</t>
+          <t>52185</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72708</t>
+          <t>73366</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76865</t>
+          <t>77746</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>106311</t>
+          <t>107194</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>518726</t>
+          <t>519014</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>537951</t>
+          <t>538659</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>472020</t>
+          <t>471362</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>493788</t>
+          <t>492543</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>997692</t>
+          <t>996809</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1027138</t>
+          <t>1026257</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,96%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23365</t>
+          <t>23816</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40649</t>
+          <t>40671</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18533</t>
+          <t>18165</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>76786</t>
+          <t>75747</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42206</t>
+          <t>36190</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>105329</t>
+          <t>104227</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>326079</t>
+          <t>326057</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>343363</t>
+          <t>342912</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>531423</t>
+          <t>532462</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>589676</t>
+          <t>590044</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>869608</t>
+          <t>870710</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>932731</t>
+          <t>938747</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25302</t>
+          <t>25787</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40872</t>
+          <t>41851</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>87761</t>
+          <t>86634</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>111212</t>
+          <t>110293</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>117821</t>
+          <t>118365</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>148170</t>
+          <t>150295</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>241887</t>
+          <t>240908</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>257457</t>
+          <t>256972</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>314619</t>
+          <t>315538</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>338070</t>
+          <t>339197</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>560420</t>
+          <t>558295</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>590769</t>
+          <t>590225</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,3%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>118258</t>
+          <t>118186</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>177835</t>
+          <t>178489</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>239466</t>
+          <t>233275</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>319636</t>
+          <t>322918</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>390812</t>
+          <t>382468</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>488338</t>
+          <t>485284</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3278587</t>
+          <t>3277933</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3338164</t>
+          <t>3338236</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3338132</t>
+          <t>3334850</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3418302</t>
+          <t>3424493</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6625852</t>
+          <t>6628906</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6723378</t>
+          <t>6731722</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1438_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1438_2023-Edad-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>9579</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9342</t>
+          <t>11954</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>310454</t>
+          <t>359616</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>303007</t>
+          <t>352933</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>710441</t>
+          <t>767409</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>703845</t>
+          <t>758351</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>6563</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2397</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15196</t>
+          <t>14691</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16391</t>
+          <t>18558</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>14549</t>
+          <t>16026</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>8548</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25756</t>
+          <t>26123</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>416826</t>
+          <t>470327</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>408351</t>
+          <t>462199</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>421150</t>
+          <t>474614</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>503676</t>
+          <t>491621</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>495113</t>
+          <t>482525</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>508027</t>
+          <t>496318</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>920502</t>
+          <t>961947</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>909295</t>
+          <t>951850</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>927627</t>
+          <t>969425</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18614</t>
+          <t>20796</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11981</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29078</t>
+          <t>31151</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>27797</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15799</t>
+          <t>19538</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30647</t>
+          <t>36645</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>41118</t>
+          <t>48593</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31643</t>
+          <t>36950</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53836</t>
+          <t>62883</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>517724</t>
+          <t>600041</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>507260</t>
+          <t>589686</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>524357</t>
+          <t>607751</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>519295</t>
+          <t>593691</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>511152</t>
+          <t>584843</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>526000</t>
+          <t>601950</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1037019</t>
+          <t>1193732</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1024301</t>
+          <t>1179442</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1046494</t>
+          <t>1205375</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078137</t>
+          <t>1242325</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078137</t>
+          <t>1242325</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078137</t>
+          <t>1242325</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32679</t>
+          <t>36054</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13511</t>
+          <t>25686</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51704</t>
+          <t>49745</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48701</t>
+          <t>53640</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37557</t>
+          <t>43896</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59632</t>
+          <t>65199</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>81380</t>
+          <t>89694</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50360</t>
+          <t>75929</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105726</t>
+          <t>108713</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>855107</t>
+          <t>664563</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>836082</t>
+          <t>650872</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>874275</t>
+          <t>674931</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>663797</t>
+          <t>682855</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>652866</t>
+          <t>671296</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>674941</t>
+          <t>692599</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1518905</t>
+          <t>1347418</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1494559</t>
+          <t>1328399</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1549925</t>
+          <t>1361183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>94,72%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>29779</t>
+          <t>31989</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20616</t>
+          <t>22935</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40261</t>
+          <t>43654</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>61253</t>
+          <t>66766</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52185</t>
+          <t>56373</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73366</t>
+          <t>79893</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>91032</t>
+          <t>98755</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77746</t>
+          <t>84737</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107194</t>
+          <t>115386</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>529496</t>
+          <t>575372</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>519014</t>
+          <t>563707</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>538659</t>
+          <t>584426</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>483475</t>
+          <t>539999</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>471362</t>
+          <t>526872</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>492543</t>
+          <t>550392</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1012971</t>
+          <t>1115371</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>996809</t>
+          <t>1098740</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1026257</t>
+          <t>1129389</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,02%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>559275</t>
+          <t>607361</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>559275</t>
+          <t>607361</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>559275</t>
+          <t>607361</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544728</t>
+          <t>606765</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544728</t>
+          <t>606765</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544728</t>
+          <t>606765</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1104003</t>
+          <t>1214126</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1104003</t>
+          <t>1214126</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1104003</t>
+          <t>1214126</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31571</t>
+          <t>32628</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23816</t>
+          <t>24566</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40671</t>
+          <t>42292</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>47730</t>
+          <t>52316</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18165</t>
+          <t>43446</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>75747</t>
+          <t>63885</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>79301</t>
+          <t>84944</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36190</t>
+          <t>71644</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>104227</t>
+          <t>98022</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>335157</t>
+          <t>372712</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>326057</t>
+          <t>363048</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>342912</t>
+          <t>380774</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>560479</t>
+          <t>386182</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>532462</t>
+          <t>374613</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>590044</t>
+          <t>395052</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>895636</t>
+          <t>758894</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>870710</t>
+          <t>745816</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>938747</t>
+          <t>772194</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>91,51%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>366728</t>
+          <t>405340</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>366728</t>
+          <t>405340</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>366728</t>
+          <t>405340</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608209</t>
+          <t>438498</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608209</t>
+          <t>438498</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608209</t>
+          <t>438498</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>974937</t>
+          <t>843838</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>974937</t>
+          <t>843838</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>974937</t>
+          <t>843838</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>33364</t>
+          <t>35698</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25787</t>
+          <t>27740</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41851</t>
+          <t>45356</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>98578</t>
+          <t>105458</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>86634</t>
+          <t>92263</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>110293</t>
+          <t>119381</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>131942</t>
+          <t>141156</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>118365</t>
+          <t>125600</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>150295</t>
+          <t>159590</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>249395</t>
+          <t>274500</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>240908</t>
+          <t>264842</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>256972</t>
+          <t>282458</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>327253</t>
+          <t>359151</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>315538</t>
+          <t>345228</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>339197</t>
+          <t>372346</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>576648</t>
+          <t>633651</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>558295</t>
+          <t>615217</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>590225</t>
+          <t>649207</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,79%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>152728</t>
+          <t>163729</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>118186</t>
+          <t>142231</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>178489</t>
+          <t>187382</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>289340</t>
+          <t>318334</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>233275</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>322918</t>
+          <t>346789</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>442068</t>
+          <t>482063</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>382468</t>
+          <t>448195</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>485284</t>
+          <t>519194</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3303694</t>
+          <t>3365308</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3277933</t>
+          <t>3341655</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3338236</t>
+          <t>3386806</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3368428</t>
+          <t>3413116</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3334850</t>
+          <t>3384661</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3424493</t>
+          <t>3436084</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6672122</t>
+          <t>6778424</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6628906</t>
+          <t>6741293</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6731722</t>
+          <t>6812292</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>93,83%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3456422</t>
+          <t>3529037</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3456422</t>
+          <t>3529037</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3456422</t>
+          <t>3529037</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3657768</t>
+          <t>3731450</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3657768</t>
+          <t>3731450</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3657768</t>
+          <t>3731450</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7114190</t>
+          <t>7260487</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7114190</t>
+          <t>7260487</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7114190</t>
+          <t>7260487</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
